--- a/Meso03_Plan.xlsx
+++ b/Meso03_Plan.xlsx
@@ -2064,8 +2064,10 @@
       <c r="A25" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>65</v>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Warm-up ramps: 1–2 ramp sets, not logged; then all working sets at one weight. Logged sets are working sets (keeps sessions ~50 min).</t>
+        </is>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -2581,7 +2583,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -2681,8 +2683,10 @@
       <c r="D6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>13</v>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>4×6 @ RPE 6–7 · Start ~185 lb</t>
+        </is>
       </c>
       <c r="F6" s="18" t="s">
         <v>18</v>
@@ -2693,8 +2697,10 @@
       <c r="H6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="18" t="s">
-        <v>119</v>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>1–2 ramp sets, not logged; then all working sets at one weight; double overhand</t>
+        </is>
       </c>
       <c r="J6" s="18" t="s">
         <v>117</v>
@@ -2713,8 +2719,10 @@
       <c r="D7" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>122</v>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>3×8–10/leg · Start ~25 lb each hand</t>
+        </is>
       </c>
       <c r="F7" s="12" t="s">
         <v>123</v>
@@ -2745,8 +2753,10 @@
       <c r="D8" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>14</v>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>3×8–10 · Start light — find it</t>
+        </is>
       </c>
       <c r="F8" s="12" t="s">
         <v>19</v>
@@ -2809,8 +2819,10 @@
       <c r="D10" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>140</v>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>2×40 yd/side · Start ~45 lb/side</t>
+        </is>
       </c>
       <c r="F10" s="12" t="s">
         <v>140</v>
@@ -2905,8 +2917,10 @@
       <c r="D13" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>13</v>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>4×6 @ RPE 6–7 · Start ~135–145 lb</t>
+        </is>
       </c>
       <c r="F13" s="18" t="s">
         <v>18</v>
@@ -2917,8 +2931,10 @@
       <c r="H13" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="18" t="s">
-        <v>149</v>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Hands on handles; no barbell grip; 1–2 ramp sets, not logged; then all working sets at one weight</t>
+        </is>
       </c>
       <c r="J13" s="20" t="s">
         <v>130</v>
@@ -2937,8 +2953,10 @@
       <c r="D14" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>133</v>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>3×8–10/side · Start ~40–45 lb</t>
+        </is>
       </c>
       <c r="F14" s="12" t="s">
         <v>134</v>
@@ -2969,8 +2987,10 @@
       <c r="D15" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>133</v>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>3×8–10/side · Start ~12.5–15 lb</t>
+        </is>
       </c>
       <c r="F15" s="12" t="s">
         <v>134</v>
@@ -3001,8 +3021,10 @@
       <c r="D16" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>14</v>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>3×8–10 · Start ~12.5–15 lb</t>
+        </is>
       </c>
       <c r="F16" s="12" t="s">
         <v>19</v>
@@ -3033,8 +3055,10 @@
       <c r="D17" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>157</v>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2×20–30 s/side · Start 5 lb</t>
+        </is>
       </c>
       <c r="F17" s="12" t="s">
         <v>157</v>
@@ -3129,8 +3153,10 @@
       <c r="D20" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>13</v>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>4×6 @ RPE 6–7 · Start ~135 lb</t>
+        </is>
       </c>
       <c r="F20" s="18" t="s">
         <v>18</v>
@@ -3141,8 +3167,10 @@
       <c r="H20" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="18" t="s">
-        <v>164</v>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>Barbell; 1–2 ramp sets, not logged; then all working sets at one weight</t>
+        </is>
       </c>
       <c r="J20" s="18" t="s">
         <v>165</v>
@@ -3161,8 +3189,10 @@
       <c r="D21" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>133</v>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>3×8–10/side · Start ~40–45 lb</t>
+        </is>
       </c>
       <c r="F21" s="12" t="s">
         <v>134</v>
@@ -3257,8 +3287,10 @@
       <c r="D24" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>140</v>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>2×40 yd/side · Start ~45 lb/side</t>
+        </is>
       </c>
       <c r="F24" s="12" t="s">
         <v>140</v>
@@ -3321,8 +3353,10 @@
       <c r="D26" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>175</v>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>3×10 · 3 s lower · Start ~180–200 lb</t>
+        </is>
       </c>
       <c r="F26" s="12" t="s">
         <v>176</v>
@@ -3528,6 +3562,41 @@
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Loading (shown in the app on every Meso 03 lift day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Main lifts: all sets at RPE 7 or easier → add 5 lb next week (Rack Pull 10 lb). 1–2 ramp sets, not logged; then all working sets at one weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Accessories: stay at one weight until every set hits the top of the rep range, then go up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Single-arm: right side sets the load; left matches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Baseline (wk 1–2) starting weights are the "Start" values in column E. First working set RPE 8+ → drop 10%. RPE 5 → add 5–10 lb. Saturday (cap 7/10): first working set above 7/10 → drop 10%. From week 3, the app's Last time line takes over.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4966,8 +5035,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
-        <v>314</v>
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Main lifts note: 1–2 ramp sets, not logged; then all working sets at one weight. Logged sets are working sets.</t>
+        </is>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
